--- a/DataframeFundos.xlsx
+++ b/DataframeFundos.xlsx
@@ -29,10 +29,10 @@
     <t>Ano</t>
   </si>
   <si>
-    <t>Alaska Black (%)</t>
+    <t>AlaskaBlack</t>
   </si>
   <si>
-    <t>Dynamo Cougar (%)</t>
+    <t>DynamoCougar</t>
   </si>
 </sst>
 </file>
